--- a/AlcanceProducción.xlsx
+++ b/AlcanceProducción.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RP\donssonImpProduccion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DONSSON\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6CE5610F-D16C-4C62-A8B4-2CE3E759860F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C6E9DE-86AF-4E4B-AE88-859A15279459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{F7EF0607-0985-4E51-B660-99D3760A7ED6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F7EF0607-0985-4E51-B660-99D3760A7ED6}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Diccionario " sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="101">
   <si>
     <t>FUNCIONALIDAD</t>
   </si>
@@ -55,13 +55,318 @@
   </si>
   <si>
     <t>SALIDAS</t>
+  </si>
+  <si>
+    <t>Registro de tiempos por centro de trabajo.</t>
+  </si>
+  <si>
+    <t>REGLAS</t>
+  </si>
+  <si>
+    <t>El sistema solo permitirá el registro de tiempo en una única OP a la vez</t>
+  </si>
+  <si>
+    <t>operario de producción</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El operario debe terminar la OP para poder iniciar otra exepto para las OP de inyeccion </t>
+  </si>
+  <si>
+    <t>Sigla/Palabra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Significado </t>
+  </si>
+  <si>
+    <t>OP</t>
+  </si>
+  <si>
+    <t>Orden de produccion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El usuario ingresa al portal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">El usuario selecciona el centro de trabajo </t>
+  </si>
+  <si>
+    <t>El sistema muestra una lista de todas las órdenes de producción activas en ese centro</t>
+  </si>
+  <si>
+    <t>El operario registra el tiempo total de cada una de las ordenes realizadas.</t>
+  </si>
+  <si>
+    <t>El sistema asigna el tiempo total de la jornada de forma equitativa a cada OP, basándose en la duración registrada.</t>
+  </si>
+  <si>
+    <t>EXCEPCIONES</t>
+  </si>
+  <si>
+    <t>Si un operario ha iniciado el registro de tiempo en la OP "A" e   intenta iniciar el registro de tiempo en la OP "B" el sistema genera una "alerta" (Complete primero la Op "A" para iniciar la OP "B".</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El sistema debe permitir registro de tiempos de OP que no esten asignadas </t>
+  </si>
+  <si>
+    <t>Costeo de producción integrado y personalizado</t>
+  </si>
+  <si>
+    <t>Analista contable</t>
+  </si>
+  <si>
+    <t>El sistema calculará el costo de los productos fabricados en función de los materiales consumidos, los tiempos de mano de obra y los costos indirectos de fabricación.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIF </t>
+  </si>
+  <si>
+    <t>Código de Identificación Fiscal</t>
+  </si>
+  <si>
+    <t>Los CIF se configurarán como costos fijos y se vincularán al proceso de producción, distribuyéndose proporcionalmente entre las órdenes en función del tiempo de ejecución.</t>
+  </si>
+  <si>
+    <t>El sistema permitirá aplicar CIF variables y fijos todos los meses, además de generar asientos contables independientes para la materia prima y la mano de obra.</t>
+  </si>
+  <si>
+    <t>Se configura el costo por hora del operario (incluyendo salario, prestaciones y comisiones).</t>
+  </si>
+  <si>
+    <t>Posteriormente se realizara el cierra OP.</t>
+  </si>
+  <si>
+    <t>El sistema costea la mano de obra multiplicando el costo por hora del operario por el tiempo efectivo registrado en la orden</t>
+  </si>
+  <si>
+    <t>costos indirectos</t>
+  </si>
+  <si>
+    <t>Configurar costos indirectos como parte de la lista de materiales o la ruta de producción</t>
+  </si>
+  <si>
+    <t>Al costear una Orden de Producción el sistema asigna el valor de los CIF a la orden, prorrateándolo según el tiempo de ejecución.</t>
+  </si>
+  <si>
+    <t>Cuando finaliza una etapa de la Orden de Producción se accede al detalle de costos</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> El sistema muestra el costo real vs. el costo planificado, identificando las variaciones por materiales, mano de obra y CIF.</t>
+  </si>
+  <si>
+    <t>Cierre parcial de órdenes de producción y merma.</t>
+  </si>
+  <si>
+    <t>Director de producción</t>
+  </si>
+  <si>
+    <t>El usuario finaliza la orden e ingresa la cantidad real producida</t>
+  </si>
+  <si>
+    <t>finalizar una orden de producción con una cantidad diferente a la planificada y reportar defectos. Para reflejar con precisión la cantidad real producida, sin que el sistema lo clasifique
+erróneamente como merma, y tener un control claro sobre los productos defectuosos Gestión de Cantidades y Calidad
+El sistema ofrece flexibilidad en el cierre de órdenes de producción (OP), permitiendo registrar la cantidad real producida aunque difiera de la original.
+Control de Defectuosos: Se permite el registro de productos no conformes, los cuales se trasladan automáticamente a una ubicación virtual de inventario.
+Análisis de Desviaciones: Esta distinción permite justificar de forma exacta las diferencias de stock, separando claramente la merma (desperdicio físico) de los errores de planificación teórica. Reporte de Recursos y Materiales
+El sistema optimiza el flujo de información contable y operativa mediante las siguientes reglas:
+Mano de Obra: Se habilita el reporte de horas de forma parcial al cierre de mes, garantizando que los costos se registren en el periodo correcto aunque la OP siga abierta.
+Materia Prima: La asignación de insumos no es automática; se realiza al finalizar el centro de producción y debe ser introducida manualmente por el supervisor.
+Nota clave: El sistema prioriza la trazabilidad del inventario defectuoso y la precisión en el reporte de costos laborales mensuales.</t>
+  </si>
+  <si>
+    <t>Cuando se  fabrica una cantidad menor o mayor a la planificada en una OP.</t>
+  </si>
+  <si>
+    <t>El sistema registra la cantidad real y actualiza el inventario de productos terminados con ese número.</t>
+  </si>
+  <si>
+    <t>Cuando se identifican productos con defectos en el proceso.</t>
+  </si>
+  <si>
+    <t>El sistema permite registrar la cantidad de productos defectuosos y los mueve a una ubicación específica ("Defectuosos"), separándolos del inventario de productos terminados</t>
+  </si>
+  <si>
+    <t>Alertas de desviación de costo y consumo</t>
+  </si>
+  <si>
+    <t>Recibir alertas cuando una orden de producción muestre un consumo de materiales o un tiempo de ejecución superior al estándar. Para intervenir de inmediato, investigar la causa de la desviación y evitar que se finalice una orden con costos excesivos.</t>
+  </si>
+  <si>
+    <t>El operario registra el consumo de materia prima de una orden en curso.</t>
+  </si>
+  <si>
+    <t>El consumo reportado supera o queda por debajo del consumo planificado.</t>
+  </si>
+  <si>
+    <t>EL sistema genera una alerta al supervisor de producción, solicitando una aprobación para continuar o corregir el registro</t>
+  </si>
+  <si>
+    <t>Al registrar el consumo de materiales o el tiempo de una orden el sistema evaluara si la desviación supera un umbral predefinido. El sistema debe generar alerta al supervisor "El material usado supera el planificado" o "El tiempo reportado supera el umbral" y el supervisor podra aprobar o corregir el registro.</t>
+  </si>
+  <si>
+    <t>Cuando el operario intenta finalizar la orden</t>
+  </si>
+  <si>
+    <t>El sistema muestra una alerta al supervisor, impidiendo el cierre de la orden hasta que la desviación sea justificada y aprobada.</t>
+  </si>
+  <si>
+    <t>Si el tiempo de ejecución de una orden supera o queda por debajo del tiempo estándar configurado</t>
+  </si>
+  <si>
+    <t>Gestión de órdenes de producción en lote</t>
+  </si>
+  <si>
+    <t>Planeador de producción</t>
+  </si>
+  <si>
+    <t>Generar y gestionar múltiples órdenes de producción de forma masiva para la planificación semanal. Para agilizar el proceso de trabajo, garantizar que todas las órdenes se creen con la información correcta y evitar la creación manual una por una.</t>
+  </si>
+  <si>
+    <t>Se generara un número de OP único de forma automática para cada una de las órdenes incluidas en el lote. El número de la orden de producción será un numero con el formato año-mes-consecutivo, el consecutivo se reinicia de forma mensual.</t>
+  </si>
+  <si>
+    <t>Utilizara la función de "Tandas" para seleccionar los productos y cantidades a fabricar.</t>
+  </si>
+  <si>
+    <t>EL sistema creara automáticamente las OP individuales y asigna un número de OP único y consecutivo a cada una.</t>
+  </si>
+  <si>
+    <t>Se ha creado una tanda de producción.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se confirma el lote de órdenes. </t>
+  </si>
+  <si>
+    <t>El sistema valida que cada orden tenga una lista de materiales (BoM) y una ruta de producción válidas, y que no existan duplicados.</t>
+  </si>
+  <si>
+    <t>BoM</t>
+  </si>
+  <si>
+    <t>Bill of Materials o Lista de Materiales</t>
+  </si>
+  <si>
+    <t>El planeador de producción crea las órdenes semanales.</t>
+  </si>
+  <si>
+    <t>Trazabilidad del inventario en proceso</t>
+  </si>
+  <si>
+    <t>Planeador de compras</t>
+  </si>
+  <si>
+    <t>El sistema facilita la reserva de inventario para ofrecer una visión clara y en tiempo real de la materia prima. Esto permite evitar quiebres de stock, planificar compras con precisión y garantizar que los materiales ya comprometidos en producción no generen conflictos operativos</t>
+  </si>
+  <si>
+    <t>Si se inicializa otra OP con la materia prima limitada, el sistema permitirá la apertura, pero la reserva se asignará por orden de confirmación, dejando la OP restante en estado "Pendiente materia prima".</t>
+  </si>
+  <si>
+    <t>Esta funcionalidad mostrara de forma clara qué inventario está disponible para nuevas operaciones y cuál está comprometido para órdenes en curso.</t>
+  </si>
+  <si>
+    <t>La orden de producción ha sido confirmada</t>
+  </si>
+  <si>
+    <t>El planeador de compras consulta el inventario de una materia prima.</t>
+  </si>
+  <si>
+    <t>El sistema mostrara la cantidad "disponible" (sin reservas) y la cantidad "pronosticada" (incluyendo lo reservado), proporcionando una visión completa de la situación del stock.</t>
+  </si>
+  <si>
+    <t>se consulta el inventario físico de la bodega</t>
+  </si>
+  <si>
+    <t>El sistema mostrara que el stock físico coincide con el stock sistémico disponible para otras operaciones, ya que el material se ha movido a un estado "reservado".</t>
+  </si>
+  <si>
+    <t>Planificación de capacidad de producción.</t>
+  </si>
+  <si>
+    <t>Gerente de planta.</t>
+  </si>
+  <si>
+    <t>Tener una herramienta visual como el diagrama de Gantt para programar las órdenes de producción según la capacidad de cada centro de trabajo. optimizar el uso de las máquinas y los recursos, balancear la carga de trabajo y detectar posibles cuellos de botella.</t>
+  </si>
+  <si>
+    <t>Se configurará el sistema para que el gerente de planta pueda ver la carga de trabajo de cada centro de producción, arrastrar y soltar órdenes para reprogramarlas, y recibir alertas si se supera la capacidad.</t>
+  </si>
+  <si>
+    <t>El gerente de planta abre el menú de planificación</t>
+  </si>
+  <si>
+    <t>Se muestra el calendario o el diagrama de Gantt.</t>
+  </si>
+  <si>
+    <t>Podra visualizar las órdenes de producción asignadas a cada centro de trabajo, mostrando la carga de tiempo estimada y la capacidad de cada centro.</t>
+  </si>
+  <si>
+    <t>Se finaliza la Orden de Producción</t>
+  </si>
+  <si>
+    <t>Se asigna una nueva orden de producción a un centro de trabajo.</t>
+  </si>
+  <si>
+    <t>Cuando la carga excede la capacidad del centro.</t>
+  </si>
+  <si>
+    <t>El sistema muestra una alerta visual para indicar un posible cuello de botella, permitiendo una fácil reasignación.</t>
+  </si>
+  <si>
+    <t>Al superar la capacidad de carga de trabajo el sistema debe mostrar una alerta visual "capacidad maxima"  y procede a una autorización manual o reprogramación.</t>
+  </si>
+  <si>
+    <t>Registro de tiempos que no están asignados a una OP</t>
+  </si>
+  <si>
+    <t>operario de producción.</t>
+  </si>
+  <si>
+    <t>diagrama de Gantt</t>
+  </si>
+  <si>
+    <r>
+      <t>herramienta visual de gestión de proyectos que ilustra el cronograma de actividades, mostrando tareas, duraciones, dependencias y responsables a lo largo del tiempo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. </t>
+    </r>
+  </si>
+  <si>
+    <t>El sistema le permitira registrar tiempos de inicio y fin que no esatn vinculados a una OP contabilizar el tiempo de forma precisa y asegurar la trazabilidad del uso del mismo.</t>
+  </si>
+  <si>
+    <t>La funcionalidad permitirá a los operarios, través de una interfaz de Odoo accesible en cada centro de trabajo, registrar el tiempo de inicio y fin de sus tareas en diferentes OP.</t>
+  </si>
+  <si>
+    <t>El sistema solo permitirá el registro de tiempo en una única OP u OTRA TAREA a la vez, obligando al operario a finalizar la tarea actual antes de comenzar en otra.</t>
+  </si>
+  <si>
+    <t>Solo se permitirá trabajar en varias OPs al mismo tiempo en inyección.</t>
+  </si>
+  <si>
+    <t>Costeo de producción integrado y personalizado de “Otras Tareas</t>
+  </si>
+  <si>
+    <t>Analista contable.</t>
+  </si>
+  <si>
+    <t>Odoo costeara las otras tareas de producción de forma automática y precisa. Para obtener el costo real de la(s) Otra(s) Tarea(s), incluyendo el salario del operario, las comisiones, puntos y las prestaciones sociales y los costos indirectos de fabricación (CIF), y asegurar la integridad contable.</t>
+  </si>
+  <si>
+    <t>El director de producción y/o gerente de Planta luego de revisar los moverán o enviarán a una Ubicación Virtual y automáticamente el sistema genera los asientos contables.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -72,6 +377,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -98,9 +423,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -435,34 +784,607 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84DA768A-41DB-45C5-A0D4-853A200E9210}">
-  <dimension ref="C3:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:J46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.28515625" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" style="5" customWidth="1"/>
+    <col min="5" max="5" width="67" style="5" customWidth="1"/>
+    <col min="6" max="6" width="33" style="3" customWidth="1"/>
+    <col min="7" max="7" width="32.7109375" style="5" customWidth="1"/>
+    <col min="8" max="8" width="43.28515625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="24.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.45">
-      <c r="C3" s="1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
+    </row>
+    <row r="2" spans="1:10" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+    </row>
+    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="F3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+    </row>
+    <row r="4" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" spans="1:10" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="F6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+    </row>
+    <row r="7" spans="1:10" ht="126" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+    </row>
+    <row r="8" spans="1:10" s="6" customFormat="1" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="5"/>
+    </row>
+    <row r="9" spans="1:10" s="6" customFormat="1" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="5"/>
+    </row>
+    <row r="10" spans="1:10" s="6" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" s="5"/>
+    </row>
+    <row r="11" spans="1:10" s="6" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="5"/>
+    </row>
+    <row r="12" spans="1:10" s="6" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12" s="5"/>
+    </row>
+    <row r="13" spans="1:10" s="6" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" s="6" customFormat="1" ht="249" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" s="6" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" s="6" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="3:8" s="6" customFormat="1" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="3:8" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="3:8" s="6" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F19" s="5"/>
+      <c r="G19" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="3:8" s="6" customFormat="1" ht="114" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="3:8" s="6" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="3:8" s="6" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="3:8" s="6" customFormat="1" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="3:8" s="6" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="3:8" s="6" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="3:8" s="6" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" spans="3:8" s="6" customFormat="1" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" spans="3:8" s="6" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="H28" s="5"/>
+    </row>
+    <row r="29" spans="3:8" s="6" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" spans="3:8" s="6" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H30" s="5"/>
+    </row>
+    <row r="31" spans="3:8" s="6" customFormat="1" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H31" s="5"/>
+    </row>
+    <row r="32" spans="3:8" s="6" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" spans="3:8" s="6" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H33" s="5"/>
+    </row>
+    <row r="34" spans="3:8" s="6" customFormat="1" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H34" s="5"/>
+    </row>
+    <row r="35" spans="3:8" s="6" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H35" s="5"/>
+    </row>
+    <row r="36" spans="3:8" s="6" customFormat="1" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H36" s="5"/>
+    </row>
+    <row r="37" spans="3:8" s="6" customFormat="1" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="3:8" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G38" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" spans="3:8" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G39" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40" spans="3:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G40" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41" spans="3:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G41" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="42" spans="3:8" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G42" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="43" spans="3:8" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44" spans="3:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F44" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45" spans="3:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="C45" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="F46" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45BA89DB-3BD8-43A9-9A38-892EC8A12063}">
+  <dimension ref="B5:D10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.42578125" style="5"/>
+    <col min="3" max="3" width="26.140625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="51.42578125" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B5" s="8"/>
+      <c r="C5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="8"/>
+      <c r="C6" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B7" s="8"/>
+      <c r="C7" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="8"/>
+      <c r="C8" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="63" x14ac:dyDescent="0.25">
+      <c r="B9" s="8"/>
+      <c r="C9" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="8"/>
+      <c r="C10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/AlcanceProducción.xlsx
+++ b/AlcanceProducción.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DONSSON\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RP\donssonImpProduccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C6E9DE-86AF-4E4B-AE88-859A15279459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC356A1-31C3-4CA9-9C99-EE9B70E5C01B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F7EF0607-0985-4E51-B660-99D3760A7ED6}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{F7EF0607-0985-4E51-B660-99D3760A7ED6}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
-    <sheet name="Diccionario " sheetId="2" r:id="rId2"/>
+    <sheet name="Especificación" sheetId="1" r:id="rId1"/>
+    <sheet name="Observaciones" sheetId="3" r:id="rId2"/>
+    <sheet name="Diccionario " sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="109">
   <si>
     <t>FUNCIONALIDAD</t>
   </si>
@@ -118,9 +119,6 @@
   </si>
   <si>
     <t xml:space="preserve">CIF </t>
-  </si>
-  <si>
-    <t>Código de Identificación Fiscal</t>
   </si>
   <si>
     <t>Los CIF se configurarán como costos fijos y se vincularán al proceso de producción, distribuyéndose proporcionalmente entre las órdenes en función del tiempo de ejecución.</t>
@@ -359,7 +357,34 @@
     <t>Odoo costeara las otras tareas de producción de forma automática y precisa. Para obtener el costo real de la(s) Otra(s) Tarea(s), incluyendo el salario del operario, las comisiones, puntos y las prestaciones sociales y los costos indirectos de fabricación (CIF), y asegurar la integridad contable.</t>
   </si>
   <si>
-    <t>El director de producción y/o gerente de Planta luego de revisar los moverán o enviarán a una Ubicación Virtual y automáticamente el sistema genera los asientos contables.</t>
+    <t>Dudas</t>
+  </si>
+  <si>
+    <t>Otras tareas</t>
+  </si>
+  <si>
+    <t>El director de producción y/o gerente de Planta luego de revisar las otras tareas las moverán o enviarán a una Ubicación Virtual y automáticamente el sistema genera los asientos contables.</t>
+  </si>
+  <si>
+    <t>Ubicación virtual de otras tareas</t>
+  </si>
+  <si>
+    <t>Costos Indirectos de fabricación</t>
+  </si>
+  <si>
+    <t>Observaciones puntuales</t>
+  </si>
+  <si>
+    <t>Funcionalidad: costeo de producción integrado y personalizado</t>
+  </si>
+  <si>
+    <t>En el escenario 1 se menciona que los costos de los operarios se pueden ver al cierre de una orden de producción, debe ser al cierre de cada centro de producción (Etapa ej:corte )</t>
+  </si>
+  <si>
+    <t>Funcionalidad: Cierre parcial de ordenes de producción y merma</t>
+  </si>
+  <si>
+    <t>En la descripcion se menciona que el sistema permitirá reportar la mano de obra de forma parcial a final de mes, se requiere que no sea solo la mano de obra , es importante que también se cierren parcialmente los CIF.</t>
   </si>
 </sst>
 </file>
@@ -785,21 +810,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84DA768A-41DB-45C5-A0D4-853A200E9210}">
   <dimension ref="A1:J46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="6.28515625" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" style="5" customWidth="1"/>
+    <col min="1" max="1" width="6.265625" customWidth="1"/>
+    <col min="2" max="2" width="5.73046875" customWidth="1"/>
+    <col min="3" max="3" width="24.73046875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="18.73046875" style="5" customWidth="1"/>
     <col min="5" max="5" width="67" style="5" customWidth="1"/>
     <col min="6" max="6" width="33" style="3" customWidth="1"/>
-    <col min="7" max="7" width="32.7109375" style="5" customWidth="1"/>
-    <col min="8" max="8" width="43.28515625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="32.73046875" style="5" customWidth="1"/>
+    <col min="8" max="8" width="43.265625" style="5" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="24.28515625" customWidth="1"/>
+    <col min="10" max="10" width="24.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C1" s="4" t="s">
         <v>0</v>
       </c>
@@ -825,7 +850,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="46.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="5" t="s">
@@ -835,7 +860,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>8</v>
@@ -846,7 +871,7 @@
       <c r="I2" s="6"/>
       <c r="J2" s="6"/>
     </row>
-    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="F3" s="5" t="s">
@@ -858,7 +883,7 @@
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
     </row>
-    <row r="4" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="F4" s="5"/>
@@ -868,7 +893,7 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
     </row>
-    <row r="5" spans="1:10" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="71.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="F5" s="5"/>
@@ -878,7 +903,7 @@
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
     </row>
-    <row r="6" spans="1:10" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="87" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="F6" s="5" t="s">
@@ -893,211 +918,218 @@
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
     </row>
-    <row r="7" spans="1:10" ht="126" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="87" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="5" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="1:10" s="6" customFormat="1" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5" t="s">
+    <row r="8" spans="1:10" ht="87" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="F8" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+    </row>
+    <row r="9" spans="1:10" ht="126" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" spans="1:10" s="6" customFormat="1" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" s="5"/>
-    </row>
-    <row r="10" spans="1:10" s="6" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="1:10" s="6" customFormat="1" ht="87" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
+      <c r="F10" s="5" t="s">
+        <v>28</v>
+      </c>
       <c r="G10" s="5" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H10" s="5"/>
     </row>
-    <row r="11" spans="1:10" s="6" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" s="6" customFormat="1" ht="69.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H11" s="5"/>
     </row>
-    <row r="12" spans="1:10" s="6" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" s="6" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H12" s="5"/>
     </row>
-    <row r="13" spans="1:10" s="6" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" s="6" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="H13" s="5"/>
     </row>
-    <row r="14" spans="1:10" s="6" customFormat="1" ht="249" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>41</v>
-      </c>
+    <row r="14" spans="1:10" s="6" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="H14" s="5"/>
     </row>
-    <row r="15" spans="1:10" s="6" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" s="6" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" s="6" customFormat="1" ht="249" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16" spans="1:10" s="6" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H16" s="5"/>
     </row>
-    <row r="17" spans="3:8" s="6" customFormat="1" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:8" s="6" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H17" s="5"/>
     </row>
-    <row r="18" spans="3:8" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:8" s="6" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="H18" s="5"/>
     </row>
-    <row r="19" spans="3:8" s="6" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:8" s="6" customFormat="1" ht="64.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H19" s="5"/>
     </row>
-    <row r="20" spans="3:8" s="6" customFormat="1" ht="114" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C20" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>47</v>
-      </c>
+    <row r="20" spans="3:8" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="3:8" s="6" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
+        <v>83</v>
+      </c>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="3:8" s="6" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F21" s="5"/>
       <c r="G21" s="5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H21" s="5"/>
     </row>
-    <row r="22" spans="3:8" s="6" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
+    <row r="22" spans="3:8" s="6" customFormat="1" ht="114" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C22" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H22" s="5"/>
-    </row>
-    <row r="23" spans="3:8" s="6" customFormat="1" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="3:8" s="6" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="H23" s="5"/>
     </row>
-    <row r="24" spans="3:8" s="6" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:8" s="6" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H24" s="5"/>
     </row>
-    <row r="25" spans="3:8" s="6" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:8" s="6" customFormat="1" ht="77.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -1107,213 +1139,214 @@
       </c>
       <c r="H25" s="5"/>
     </row>
-    <row r="26" spans="3:8" s="6" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C26" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>58</v>
-      </c>
+    <row r="26" spans="3:8" s="6" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
       <c r="G26" s="5" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="H26" s="5"/>
     </row>
-    <row r="27" spans="3:8" s="6" customFormat="1" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:8" s="6" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="5" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="H27" s="5"/>
     </row>
-    <row r="28" spans="3:8" s="6" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
+    <row r="28" spans="3:8" s="6" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C28" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="G28" s="5" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H28" s="5"/>
     </row>
-    <row r="29" spans="3:8" s="6" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:8" s="6" customFormat="1" ht="69.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="H29" s="5"/>
     </row>
-    <row r="30" spans="3:8" s="6" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:8" s="6" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H30" s="5"/>
     </row>
-    <row r="31" spans="3:8" s="6" customFormat="1" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:8" s="6" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="H31" s="5"/>
     </row>
-    <row r="32" spans="3:8" s="6" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>71</v>
-      </c>
+    <row r="32" spans="3:8" s="6" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
       <c r="G32" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="33" spans="3:8" s="6" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="H32" s="5"/>
+    </row>
+    <row r="33" spans="3:8" s="6" customFormat="1" ht="68.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="5" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="H33" s="5"/>
     </row>
-    <row r="34" spans="3:8" s="6" customFormat="1" ht="93" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
+    <row r="34" spans="3:8" s="6" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C34" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>70</v>
+      </c>
       <c r="G34" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H34" s="5"/>
-    </row>
-    <row r="35" spans="3:8" s="6" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="35" spans="3:8" s="6" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
       <c r="G35" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H35" s="5"/>
     </row>
-    <row r="36" spans="3:8" s="6" customFormat="1" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:8" s="6" customFormat="1" ht="93" customHeight="1" x14ac:dyDescent="0.45">
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="H36" s="5"/>
+    </row>
+    <row r="37" spans="3:8" s="6" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="H37" s="5"/>
+    </row>
+    <row r="38" spans="3:8" s="6" customFormat="1" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H38" s="5"/>
+    </row>
+    <row r="39" spans="3:8" s="6" customFormat="1" ht="114.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="C39" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="H36" s="5"/>
-    </row>
-    <row r="37" spans="3:8" s="6" customFormat="1" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="5" t="s">
+      <c r="D39" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="E39" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="F39" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="G39" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="H39" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="3:8" ht="98.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G40" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="H37" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="38" spans="3:8" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G38" s="5" t="s">
+    </row>
+    <row r="41" spans="3:8" ht="76.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G41" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="39" spans="3:8" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G39" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="40" spans="3:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G40" s="5" t="s">
+    <row r="42" spans="3:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G42" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="3:8" ht="45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G43" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="41" spans="3:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G41" s="5" t="s">
+    <row r="44" spans="3:8" ht="85.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="G44" s="5" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="42" spans="3:8" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G42" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="43" spans="3:8" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="44" spans="3:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F44" s="3" t="s">
+    <row r="45" spans="3:8" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="C45" s="5" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="45" spans="3:8" ht="90" x14ac:dyDescent="0.25">
-      <c r="C45" s="5" t="s">
+      <c r="D45" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="E45" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="E45" s="5" t="s">
-        <v>99</v>
-      </c>
       <c r="G45" s="5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" spans="3:8" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="46" spans="3:8" x14ac:dyDescent="0.45">
       <c r="F46" s="5"/>
     </row>
   </sheetData>
@@ -1323,16 +1356,51 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B14895DA-B627-4BA0-A7C5-8BC7CEE6C7D3}">
+  <dimension ref="C3:C9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="3" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C3" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="8" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45BA89DB-3BD8-43A9-9A38-892EC8A12063}">
-  <dimension ref="B5:D10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B5:D19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="11.42578125" style="5"/>
-    <col min="3" max="3" width="26.140625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="51.42578125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="11.3984375" style="5"/>
+    <col min="3" max="3" width="26.1328125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="51.3984375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="B5" s="8"/>
       <c r="C5" s="8" t="s">
         <v>11</v>
@@ -1341,7 +1409,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="B6" s="8"/>
       <c r="C6" s="8" t="s">
         <v>13</v>
@@ -1350,39 +1418,56 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="B7" s="8"/>
       <c r="C7" s="9" t="s">
         <v>26</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="B8" s="8"/>
       <c r="C8" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" ht="63" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="2:4" ht="47.25" x14ac:dyDescent="0.45">
       <c r="B9" s="8"/>
       <c r="C9" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="2:4" ht="15.75" x14ac:dyDescent="0.45">
       <c r="B10" s="8"/>
-      <c r="C10" s="8" t="s">
-        <v>33</v>
-      </c>
       <c r="D10" s="8"/>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="C16" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C17" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="C18" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.45">
+      <c r="C19" s="5" t="s">
+        <v>102</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AlcanceProducción.xlsx
+++ b/AlcanceProducción.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DONSSON\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C6E9DE-86AF-4E4B-AE88-859A15279459}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D569905-CBC9-4566-9EB8-A619A6460961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F7EF0607-0985-4E51-B660-99D3760A7ED6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F7EF0607-0985-4E51-B660-99D3760A7ED6}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -120,9 +120,6 @@
     <t xml:space="preserve">CIF </t>
   </si>
   <si>
-    <t>Código de Identificación Fiscal</t>
-  </si>
-  <si>
     <t>Los CIF se configurarán como costos fijos y se vincularán al proceso de producción, distribuyéndose proporcionalmente entre las órdenes en función del tiempo de ejecución.</t>
   </si>
   <si>
@@ -359,7 +356,10 @@
     <t>Odoo costeara las otras tareas de producción de forma automática y precisa. Para obtener el costo real de la(s) Otra(s) Tarea(s), incluyendo el salario del operario, las comisiones, puntos y las prestaciones sociales y los costos indirectos de fabricación (CIF), y asegurar la integridad contable.</t>
   </si>
   <si>
-    <t>El director de producción y/o gerente de Planta luego de revisar los moverán o enviarán a una Ubicación Virtual y automáticamente el sistema genera los asientos contables.</t>
+    <t xml:space="preserve">el Director de Producción y/o Gerente </t>
+  </si>
+  <si>
+    <t>Costos Indirectos de Fabricación</t>
   </si>
 </sst>
 </file>
@@ -835,7 +835,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>8</v>
@@ -906,10 +906,10 @@
         <v>25</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
@@ -919,10 +919,10 @@
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H8" s="5"/>
     </row>
@@ -932,7 +932,7 @@
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H9" s="5"/>
     </row>
@@ -942,7 +942,7 @@
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H10" s="5"/>
     </row>
@@ -952,7 +952,7 @@
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H11" s="5"/>
     </row>
@@ -962,7 +962,7 @@
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H12" s="5"/>
     </row>
@@ -972,23 +972,23 @@
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:10" s="6" customFormat="1" ht="249" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="E14" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H14" s="5"/>
     </row>
@@ -998,7 +998,7 @@
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H15" s="5"/>
     </row>
@@ -1008,7 +1008,7 @@
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H16" s="5"/>
     </row>
@@ -1018,7 +1018,7 @@
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H17" s="5"/>
     </row>
@@ -1028,33 +1028,33 @@
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H18" s="5"/>
     </row>
     <row r="19" spans="3:8" s="6" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F19" s="5"/>
       <c r="G19" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H19" s="5"/>
     </row>
     <row r="20" spans="3:8" s="6" customFormat="1" ht="114" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>46</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>47</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="3:8" s="6" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1063,7 +1063,7 @@
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H21" s="5"/>
     </row>
@@ -1073,7 +1073,7 @@
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H22" s="5"/>
     </row>
@@ -1083,7 +1083,7 @@
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H23" s="5"/>
     </row>
@@ -1093,7 +1093,7 @@
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H24" s="5"/>
     </row>
@@ -1103,25 +1103,25 @@
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H25" s="5"/>
     </row>
     <row r="26" spans="3:8" s="6" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="F26" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F26" s="5" t="s">
-        <v>58</v>
-      </c>
       <c r="G26" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H26" s="5"/>
     </row>
@@ -1131,7 +1131,7 @@
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H27" s="5"/>
     </row>
@@ -1141,7 +1141,7 @@
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H28" s="5"/>
     </row>
@@ -1151,7 +1151,7 @@
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H29" s="5"/>
     </row>
@@ -1161,7 +1161,7 @@
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H30" s="5"/>
     </row>
@@ -1171,28 +1171,28 @@
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H31" s="5"/>
     </row>
     <row r="32" spans="3:8" s="6" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="E32" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="F32" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H32" s="7" t="s">
         <v>69</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="33" spans="3:8" s="6" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1201,7 +1201,7 @@
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H33" s="5"/>
     </row>
@@ -1211,7 +1211,7 @@
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H34" s="5"/>
     </row>
@@ -1221,7 +1221,7 @@
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
       <c r="G35" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H35" s="5"/>
     </row>
@@ -1231,86 +1231,86 @@
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H36" s="5"/>
     </row>
     <row r="37" spans="3:8" s="6" customFormat="1" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="E37" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="F37" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="G37" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="G37" s="5" t="s">
-        <v>81</v>
-      </c>
       <c r="H37" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="3:8" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G38" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" spans="3:8" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G39" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="3:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G40" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="3:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G41" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="3:8" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G42" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="3:8" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D43" s="5" t="s">
-        <v>90</v>
-      </c>
       <c r="E43" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" spans="3:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F44" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="45" spans="3:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="C45" s="5" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="45" spans="3:8" ht="90" x14ac:dyDescent="0.25">
-      <c r="C45" s="5" t="s">
+      <c r="D45" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="E45" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="F45" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="46" spans="3:8" x14ac:dyDescent="0.25">
@@ -1356,31 +1356,31 @@
         <v>26</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B8" s="8"/>
       <c r="C8" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>64</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="63" x14ac:dyDescent="0.25">
       <c r="B9" s="8"/>
       <c r="C9" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>91</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B10" s="8"/>
       <c r="C10" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" s="8"/>
     </row>

--- a/AlcanceProducción.xlsx
+++ b/AlcanceProducción.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DONSSON\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D569905-CBC9-4566-9EB8-A619A6460961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8137C1FB-9302-425C-AA60-427E4F7167F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F7EF0607-0985-4E51-B660-99D3760A7ED6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F7EF0607-0985-4E51-B660-99D3760A7ED6}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="131">
   <si>
     <t>FUNCIONALIDAD</t>
   </si>
@@ -69,9 +69,6 @@
     <t>operario de producción</t>
   </si>
   <si>
-    <t xml:space="preserve">El operario debe terminar la OP para poder iniciar otra exepto para las OP de inyeccion </t>
-  </si>
-  <si>
     <t>Sigla/Palabra</t>
   </si>
   <si>
@@ -105,9 +102,6 @@
     <t>Si un operario ha iniciado el registro de tiempo en la OP "A" e   intenta iniciar el registro de tiempo en la OP "B" el sistema genera una "alerta" (Complete primero la Op "A" para iniciar la OP "B".</t>
   </si>
   <si>
-    <t xml:space="preserve">El sistema debe permitir registro de tiempos de OP que no esten asignadas </t>
-  </si>
-  <si>
     <t>Costeo de producción integrado y personalizado</t>
   </si>
   <si>
@@ -159,17 +153,6 @@
     <t>El usuario finaliza la orden e ingresa la cantidad real producida</t>
   </si>
   <si>
-    <t>finalizar una orden de producción con una cantidad diferente a la planificada y reportar defectos. Para reflejar con precisión la cantidad real producida, sin que el sistema lo clasifique
-erróneamente como merma, y tener un control claro sobre los productos defectuosos Gestión de Cantidades y Calidad
-El sistema ofrece flexibilidad en el cierre de órdenes de producción (OP), permitiendo registrar la cantidad real producida aunque difiera de la original.
-Control de Defectuosos: Se permite el registro de productos no conformes, los cuales se trasladan automáticamente a una ubicación virtual de inventario.
-Análisis de Desviaciones: Esta distinción permite justificar de forma exacta las diferencias de stock, separando claramente la merma (desperdicio físico) de los errores de planificación teórica. Reporte de Recursos y Materiales
-El sistema optimiza el flujo de información contable y operativa mediante las siguientes reglas:
-Mano de Obra: Se habilita el reporte de horas de forma parcial al cierre de mes, garantizando que los costos se registren en el periodo correcto aunque la OP siga abierta.
-Materia Prima: La asignación de insumos no es automática; se realiza al finalizar el centro de producción y debe ser introducida manualmente por el supervisor.
-Nota clave: El sistema prioriza la trazabilidad del inventario defectuoso y la precisión en el reporte de costos laborales mensuales.</t>
-  </si>
-  <si>
     <t>Cuando se  fabrica una cantidad menor o mayor a la planificada en una OP.</t>
   </si>
   <si>
@@ -197,9 +180,6 @@
     <t>EL sistema genera una alerta al supervisor de producción, solicitando una aprobación para continuar o corregir el registro</t>
   </si>
   <si>
-    <t>Al registrar el consumo de materiales o el tiempo de una orden el sistema evaluara si la desviación supera un umbral predefinido. El sistema debe generar alerta al supervisor "El material usado supera el planificado" o "El tiempo reportado supera el umbral" y el supervisor podra aprobar o corregir el registro.</t>
-  </si>
-  <si>
     <t>Cuando el operario intenta finalizar la orden</t>
   </si>
   <si>
@@ -293,9 +273,6 @@
     <t>Se muestra el calendario o el diagrama de Gantt.</t>
   </si>
   <si>
-    <t>Podra visualizar las órdenes de producción asignadas a cada centro de trabajo, mostrando la carga de tiempo estimada y la capacidad de cada centro.</t>
-  </si>
-  <si>
     <t>Se finaliza la Orden de Producción</t>
   </si>
   <si>
@@ -306,9 +283,6 @@
   </si>
   <si>
     <t>El sistema muestra una alerta visual para indicar un posible cuello de botella, permitiendo una fácil reasignación.</t>
-  </si>
-  <si>
-    <t>Al superar la capacidad de carga de trabajo el sistema debe mostrar una alerta visual "capacidad maxima"  y procede a una autorización manual o reprogramación.</t>
   </si>
   <si>
     <t>Registro de tiempos que no están asignados a una OP</t>
@@ -335,9 +309,6 @@
     </r>
   </si>
   <si>
-    <t>El sistema le permitira registrar tiempos de inicio y fin que no esatn vinculados a una OP contabilizar el tiempo de forma precisa y asegurar la trazabilidad del uso del mismo.</t>
-  </si>
-  <si>
     <t>La funcionalidad permitirá a los operarios, través de una interfaz de Odoo accesible en cada centro de trabajo, registrar el tiempo de inicio y fin de sus tareas en diferentes OP.</t>
   </si>
   <si>
@@ -347,9 +318,6 @@
     <t>Solo se permitirá trabajar en varias OPs al mismo tiempo en inyección.</t>
   </si>
   <si>
-    <t>Costeo de producción integrado y personalizado de “Otras Tareas</t>
-  </si>
-  <si>
     <t>Analista contable.</t>
   </si>
   <si>
@@ -360,13 +328,134 @@
   </si>
   <si>
     <t>Costos Indirectos de Fabricación</t>
+  </si>
+  <si>
+    <t>Control de Desviación de Consumos</t>
+  </si>
+  <si>
+    <t>finalizar una orden de producción con una cantidad diferente a la planificada y reportar defectos. Para reflejar con precisión la cantidad real producida, sin que el sistema lo clasifique erróneamente como merma, y tener un control claro sobre los productos defectuosos Gestión de Cantidades y Calidad
+El sistema ofrece flexibilidad en el cierre de órdenes de producción (OP), permitiendo registrar la cantidad real producida aunque difiera de la original.
+Control de Defectuosos: Se permite el registro de productos no conformes, los cuales se trasladan automáticamente a una ubicación virtual de inventario.
+Análisis de Desviaciones: Esta distinción permite justificar de forma exacta las diferencias de stock, separando claramente la merma (desperdicio físico) de los errores de planificación teórica. Reporte de Recursos y Materiales
+El sistema optimiza el flujo de información contable y operativa mediante las siguientes reglas:
+Mano de Obra: Se habilita el reporte de horas de forma parcial al cierre de mes, garantizando que los costos se registren en el periodo correcto aunque la OP siga abierta.
+Materia Prima: La asignación de insumos no es automática; se realiza al finalizar el centro de producción y debe ser introducida manualmente por el supervisor.
+Nota clave: El sistema prioriza la trazabilidad del inventario defectuoso y la precisión en el reporte de costos laborales mensuales.</t>
+  </si>
+  <si>
+    <t>Director de Producción</t>
+  </si>
+  <si>
+    <t>Validación de materia prima al cierre de OP</t>
+  </si>
+  <si>
+    <t>Bloqueo automático si el consumo real supera el umbral permitido vs. BOM</t>
+  </si>
+  <si>
+    <t>Comparación automática</t>
+  </si>
+  <si>
+    <t>Registro de cantidad final</t>
+  </si>
+  <si>
+    <t>Solicitud de aprobación si hay exceso.</t>
+  </si>
+  <si>
+    <t>Costeo de producción integrado y personalizado de “Otras Tareas"</t>
+  </si>
+  <si>
+    <t>Analista Contable</t>
+  </si>
+  <si>
+    <t>El costo se basa en segundos efectivos. Incluye carga prestacional y comisiones.</t>
+  </si>
+  <si>
+    <t>Consolidación de segundos por OP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Aplicación de tasa por segundo </t>
+  </si>
+  <si>
+    <t>Generación de costo total</t>
+  </si>
+  <si>
+    <t>Costeo de Mano de Obra y Análisis de Valor Prestacional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquidación económica de la producción con comisiones. </t>
+  </si>
+  <si>
+    <t>Identificar empleado.</t>
+  </si>
+  <si>
+    <t>Panel de Carga por Centro y Operario (Gantt/Calendario)</t>
+  </si>
+  <si>
+    <t>Programación semanal de tareas.</t>
+  </si>
+  <si>
+    <t>Ausentismo no programado o fallas mecánicas que alteren la capacidad real.</t>
+  </si>
+  <si>
+    <t>Asignar operarios según habilidad/centro.</t>
+  </si>
+  <si>
+    <t>Cargar OPs activas.</t>
+  </si>
+  <si>
+    <t>Visualizar saturación de carga en calendario.</t>
+  </si>
+  <si>
+    <t>Disparador de Reabastecimiento Automático</t>
+  </si>
+  <si>
+    <t>Jefe de Producción</t>
+  </si>
+  <si>
+    <t>Jefe de Inventarios</t>
+  </si>
+  <si>
+    <t>Generación proactiva de órdenes (Mano de Obra y Materia Prima).</t>
+  </si>
+  <si>
+    <t>Punto de reorden basado en consumo histórico (Regla del 80% o stock mínimo de seguridad).</t>
+  </si>
+  <si>
+    <t>Monitoreo de stock real</t>
+  </si>
+  <si>
+    <t>Cruce con OPs en firme.</t>
+  </si>
+  <si>
+    <t>Alerta de generación de OP/OC automática.</t>
+  </si>
+  <si>
+    <t>Picos de demanda atípicos que el historial no contempla (requiere ajuste manual).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El operario debe terminar la OP para poder iniciar otra excepto para las OP de inyección </t>
+  </si>
+  <si>
+    <t xml:space="preserve">El sistema debe permitir registro de tiempos de OP que no estén asignadas </t>
+  </si>
+  <si>
+    <t>Al registrar el consumo de materiales o el tiempo de una orden el sistema evaluara si la desviación supera un umbral predefinido. El sistema debe generar alerta al supervisor "El material usado supera el planificado" o "El tiempo reportado supera el umbral" y el supervisor podrá aprobar o corregir el registro.</t>
+  </si>
+  <si>
+    <t>Al superar la capacidad de carga de trabajo el sistema debe mostrar una alerta visual "capacidad máxima"  y procede a una autorización manual o reprogramación.</t>
+  </si>
+  <si>
+    <t>Podrá visualizar las órdenes de producción asignadas a cada centro de trabajo, mostrando la carga de tiempo estimada y la capacidad de cada centro.</t>
+  </si>
+  <si>
+    <t>El sistema le permitirá registrar tiempos de inicio y fin que no están vinculados a una OP contabilizar el tiempo de forma precisa y asegurar la trazabilidad del uso del mismo.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -383,12 +472,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF0A0A0A"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color rgb="FF0A0A0A"/>
       <name val="Aptos Narrow"/>
@@ -401,6 +484,32 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -423,12 +532,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -441,14 +546,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -784,537 +910,1091 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84DA768A-41DB-45C5-A0D4-853A200E9210}">
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J95"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.28515625" customWidth="1"/>
     <col min="2" max="2" width="5.7109375" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" style="5" customWidth="1"/>
-    <col min="5" max="5" width="67" style="5" customWidth="1"/>
-    <col min="6" max="6" width="33" style="3" customWidth="1"/>
-    <col min="7" max="7" width="32.7109375" style="5" customWidth="1"/>
-    <col min="8" max="8" width="43.28515625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="67" style="3" customWidth="1"/>
+    <col min="6" max="6" width="33" style="1" customWidth="1"/>
+    <col min="7" max="7" width="32.7109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="43.28515625" style="3" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
     <col min="10" max="10" width="24.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="15"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+    </row>
+    <row r="3" spans="1:10" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="15"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+    </row>
+    <row r="4" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="15"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+    </row>
+    <row r="5" spans="1:10" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="15"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+    </row>
+    <row r="6" spans="1:10" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+    </row>
+    <row r="7" spans="1:10" ht="126" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="15"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+    </row>
+    <row r="8" spans="1:10" s="4" customFormat="1" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="14"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="15"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+    </row>
+    <row r="9" spans="1:10" s="4" customFormat="1" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="14"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="15"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+    </row>
+    <row r="10" spans="1:10" s="4" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="14"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="15"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+    </row>
+    <row r="11" spans="1:10" s="4" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="14"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="15"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+    </row>
+    <row r="12" spans="1:10" s="4" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="14"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="15"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="1:10" s="4" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="14"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" s="15"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+    </row>
+    <row r="14" spans="1:10" s="4" customFormat="1" ht="249" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="14"/>
+      <c r="C14" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="15"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+    </row>
+    <row r="15" spans="1:10" s="4" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="14"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="15"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+    </row>
+    <row r="16" spans="1:10" s="4" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="14"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" s="15"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+    </row>
+    <row r="17" spans="2:10" s="4" customFormat="1" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="14"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="H17" s="15"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+    </row>
+    <row r="18" spans="2:10" s="4" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="14"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="H18" s="15"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+    </row>
+    <row r="19" spans="2:10" s="4" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="14"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="H19" s="15"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+    </row>
+    <row r="20" spans="2:10" s="4" customFormat="1" ht="114" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="14"/>
+      <c r="C20" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+    </row>
+    <row r="21" spans="2:10" s="4" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="14"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H21" s="15"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+    </row>
+    <row r="22" spans="2:10" s="4" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="14"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="H22" s="15"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" spans="2:10" s="4" customFormat="1" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="14"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23" s="15"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+    </row>
+    <row r="24" spans="2:10" s="4" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="14"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H24" s="15"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+    </row>
+    <row r="25" spans="2:10" s="4" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="14"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="H25" s="15"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+    </row>
+    <row r="26" spans="2:10" s="4" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="14"/>
+      <c r="C26" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="H26" s="15"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+    </row>
+    <row r="27" spans="2:10" s="4" customFormat="1" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="14"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="H27" s="15"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+    </row>
+    <row r="28" spans="2:10" s="4" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="14"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="H28" s="15"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+    </row>
+    <row r="29" spans="2:10" s="4" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="14"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="H29" s="15"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+    </row>
+    <row r="30" spans="2:10" s="4" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="14"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="H30" s="15"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+    </row>
+    <row r="31" spans="2:10" s="4" customFormat="1" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="14"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="H31" s="15"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+    </row>
+    <row r="32" spans="2:10" s="4" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="14"/>
+      <c r="C32" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+    </row>
+    <row r="33" spans="2:10" s="4" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="14"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H33" s="15"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+    </row>
+    <row r="34" spans="2:10" s="4" customFormat="1" ht="93" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="14"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="H34" s="15"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+    </row>
+    <row r="35" spans="2:10" s="4" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="14"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="H35" s="15"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+    </row>
+    <row r="36" spans="2:10" s="4" customFormat="1" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="14"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="H36" s="15"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+    </row>
+    <row r="37" spans="2:10" s="4" customFormat="1" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="14"/>
+      <c r="C37" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="G37" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+    </row>
+    <row r="38" spans="2:10" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="10"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="H38" s="15"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+    </row>
+    <row r="39" spans="2:10" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="10"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="H39" s="15"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+    </row>
+    <row r="40" spans="2:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="10"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="H40" s="15"/>
+      <c r="I40" s="10"/>
+      <c r="J40" s="10"/>
+    </row>
+    <row r="41" spans="2:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="10"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="H41" s="15"/>
+      <c r="I41" s="10"/>
+      <c r="J41" s="10"/>
+    </row>
+    <row r="42" spans="2:10" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="10"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="H42" s="15"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+    </row>
+    <row r="43" spans="2:10" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="10"/>
+      <c r="C43" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="F43" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="G43" s="15"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="10"/>
+      <c r="J43" s="10"/>
+    </row>
+    <row r="44" spans="2:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="10"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="G44" s="15"/>
+      <c r="H44" s="15"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+    </row>
+    <row r="45" spans="2:10" ht="71.25" x14ac:dyDescent="0.25">
+      <c r="B45" s="10"/>
+      <c r="C45" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="E45" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="G45" s="15"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="10"/>
+      <c r="J45" s="10"/>
+    </row>
+    <row r="46" spans="2:10" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="B46" s="10"/>
+      <c r="C46" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="F2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-    </row>
-    <row r="3" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="F3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-    </row>
-    <row r="4" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-    </row>
-    <row r="5" spans="1:10" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-    </row>
-    <row r="6" spans="1:10" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="F6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-    </row>
-    <row r="7" spans="1:10" ht="126" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-    </row>
-    <row r="8" spans="1:10" s="6" customFormat="1" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" spans="1:10" s="6" customFormat="1" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H9" s="5"/>
-    </row>
-    <row r="10" spans="1:10" s="6" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10" s="5"/>
-    </row>
-    <row r="11" spans="1:10" s="6" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="1:10" s="6" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" s="5"/>
-    </row>
-    <row r="13" spans="1:10" s="6" customFormat="1" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H13" s="5"/>
-    </row>
-    <row r="14" spans="1:10" s="6" customFormat="1" ht="249" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H14" s="5"/>
-    </row>
-    <row r="15" spans="1:10" s="6" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="H15" s="5"/>
-    </row>
-    <row r="16" spans="1:10" s="6" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H16" s="5"/>
-    </row>
-    <row r="17" spans="3:8" s="6" customFormat="1" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H17" s="5"/>
-    </row>
-    <row r="18" spans="3:8" s="6" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="H18" s="5"/>
-    </row>
-    <row r="19" spans="3:8" s="6" customFormat="1" ht="96" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F19" s="5"/>
-      <c r="G19" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="H19" s="5"/>
-    </row>
-    <row r="20" spans="3:8" s="6" customFormat="1" ht="114" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C20" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="3:8" s="6" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="H21" s="5"/>
-    </row>
-    <row r="22" spans="3:8" s="6" customFormat="1" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="H22" s="5"/>
-    </row>
-    <row r="23" spans="3:8" s="6" customFormat="1" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H23" s="5"/>
-    </row>
-    <row r="24" spans="3:8" s="6" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="H24" s="5"/>
-    </row>
-    <row r="25" spans="3:8" s="6" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="H25" s="5"/>
-    </row>
-    <row r="26" spans="3:8" s="6" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C26" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="H26" s="5"/>
-    </row>
-    <row r="27" spans="3:8" s="6" customFormat="1" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H27" s="5"/>
-    </row>
-    <row r="28" spans="3:8" s="6" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H28" s="5"/>
-    </row>
-    <row r="29" spans="3:8" s="6" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="H29" s="5"/>
-    </row>
-    <row r="30" spans="3:8" s="6" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H30" s="5"/>
-    </row>
-    <row r="31" spans="3:8" s="6" customFormat="1" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="H31" s="5"/>
-    </row>
-    <row r="32" spans="3:8" s="6" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="33" spans="3:8" s="6" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="H33" s="5"/>
-    </row>
-    <row r="34" spans="3:8" s="6" customFormat="1" ht="93" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="H34" s="5"/>
-    </row>
-    <row r="35" spans="3:8" s="6" customFormat="1" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H35" s="5"/>
-    </row>
-    <row r="36" spans="3:8" s="6" customFormat="1" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="H36" s="5"/>
-    </row>
-    <row r="37" spans="3:8" s="6" customFormat="1" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="38" spans="3:8" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G38" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="39" spans="3:8" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G39" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="40" spans="3:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G40" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="41" spans="3:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G41" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="42" spans="3:8" ht="85.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G42" s="5" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="43" spans="3:8" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="44" spans="3:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F44" s="3" t="s">
+      <c r="D46" s="8" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="45" spans="3:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="C45" s="5" t="s">
+      <c r="E46" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="F46" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="G46" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+    </row>
+    <row r="47" spans="2:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="10"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="F45" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="46" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="F46" s="5"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
+      <c r="J47" s="15"/>
+    </row>
+    <row r="48" spans="2:10" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="B48" s="10"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="H48" s="15"/>
+      <c r="I48" s="15"/>
+      <c r="J48" s="15"/>
+    </row>
+    <row r="49" spans="2:10" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="10"/>
+      <c r="C49" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="H49" s="15"/>
+      <c r="I49" s="15"/>
+      <c r="J49" s="15"/>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B50" s="10"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="15"/>
+      <c r="E50" s="15"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="H50" s="15"/>
+      <c r="I50" s="15"/>
+      <c r="J50" s="15"/>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B51" s="10"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="15"/>
+      <c r="E51" s="15"/>
+      <c r="F51" s="15"/>
+      <c r="G51" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="H51" s="15"/>
+      <c r="I51" s="15"/>
+      <c r="J51" s="15"/>
+    </row>
+    <row r="52" spans="2:10" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="B52" s="10"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="H52" s="15"/>
+      <c r="I52" s="15"/>
+      <c r="J52" s="15"/>
+    </row>
+    <row r="53" spans="2:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="B53" s="10"/>
+      <c r="C53" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="F53" s="16"/>
+      <c r="G53" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="I53" s="15"/>
+      <c r="J53" s="15"/>
+    </row>
+    <row r="54" spans="2:10" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="B54" s="10"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="15"/>
+      <c r="E54" s="15"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="H54" s="15"/>
+      <c r="I54" s="15"/>
+      <c r="J54" s="15"/>
+    </row>
+    <row r="55" spans="2:10" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="B55" s="10"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15"/>
+      <c r="J55" s="15"/>
+    </row>
+    <row r="56" spans="2:10" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="10"/>
+      <c r="C56" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="I56" s="15"/>
+      <c r="J56" s="15"/>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B57" s="10"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="15"/>
+      <c r="E57" s="15"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H57" s="15"/>
+      <c r="I57" s="15"/>
+      <c r="J57" s="15"/>
+    </row>
+    <row r="58" spans="2:10" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="B58" s="10"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="15"/>
+      <c r="E58" s="15"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="H58" s="15"/>
+      <c r="I58" s="15"/>
+      <c r="J58" s="15"/>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F59" s="3"/>
+      <c r="I59" s="3"/>
+      <c r="J59" s="3"/>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F60" s="3"/>
+      <c r="I60" s="3"/>
+      <c r="J60" s="3"/>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F61" s="3"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3"/>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3"/>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F63" s="3"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3"/>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="F64" s="3"/>
+      <c r="I64" s="3"/>
+      <c r="J64" s="3"/>
+    </row>
+    <row r="65" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F65" s="3"/>
+      <c r="I65" s="3"/>
+      <c r="J65" s="3"/>
+    </row>
+    <row r="66" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F66" s="3"/>
+      <c r="I66" s="3"/>
+      <c r="J66" s="3"/>
+    </row>
+    <row r="67" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F67" s="3"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="3"/>
+    </row>
+    <row r="68" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F68" s="3"/>
+      <c r="I68" s="3"/>
+      <c r="J68" s="3"/>
+    </row>
+    <row r="69" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F69" s="3"/>
+      <c r="I69" s="3"/>
+      <c r="J69" s="3"/>
+    </row>
+    <row r="70" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F70" s="3"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="3"/>
+    </row>
+    <row r="71" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F71" s="3"/>
+      <c r="I71" s="3"/>
+      <c r="J71" s="3"/>
+    </row>
+    <row r="72" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F72" s="3"/>
+      <c r="I72" s="3"/>
+      <c r="J72" s="3"/>
+    </row>
+    <row r="73" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F73" s="3"/>
+      <c r="I73" s="3"/>
+      <c r="J73" s="3"/>
+    </row>
+    <row r="74" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F74" s="3"/>
+      <c r="I74" s="3"/>
+      <c r="J74" s="3"/>
+    </row>
+    <row r="75" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F75" s="3"/>
+      <c r="I75" s="3"/>
+      <c r="J75" s="3"/>
+    </row>
+    <row r="76" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F76" s="3"/>
+      <c r="I76" s="3"/>
+      <c r="J76" s="3"/>
+    </row>
+    <row r="77" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F77" s="3"/>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3"/>
+    </row>
+    <row r="78" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F78" s="3"/>
+      <c r="I78" s="3"/>
+      <c r="J78" s="3"/>
+    </row>
+    <row r="79" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F79" s="3"/>
+      <c r="I79" s="3"/>
+      <c r="J79" s="3"/>
+    </row>
+    <row r="80" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F80" s="3"/>
+      <c r="I80" s="3"/>
+      <c r="J80" s="3"/>
+    </row>
+    <row r="81" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F81" s="3"/>
+      <c r="I81" s="3"/>
+      <c r="J81" s="3"/>
+    </row>
+    <row r="82" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F82" s="3"/>
+      <c r="I82" s="3"/>
+      <c r="J82" s="3"/>
+    </row>
+    <row r="83" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F83" s="3"/>
+      <c r="I83" s="3"/>
+      <c r="J83" s="3"/>
+    </row>
+    <row r="84" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F84" s="3"/>
+      <c r="I84" s="3"/>
+      <c r="J84" s="3"/>
+    </row>
+    <row r="85" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F85" s="3"/>
+      <c r="I85" s="3"/>
+      <c r="J85" s="3"/>
+    </row>
+    <row r="86" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F86" s="3"/>
+      <c r="I86" s="3"/>
+      <c r="J86" s="3"/>
+    </row>
+    <row r="87" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F87" s="3"/>
+      <c r="I87" s="3"/>
+      <c r="J87" s="3"/>
+    </row>
+    <row r="88" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F88" s="3"/>
+      <c r="I88" s="3"/>
+      <c r="J88" s="3"/>
+    </row>
+    <row r="89" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F89" s="3"/>
+      <c r="I89" s="3"/>
+      <c r="J89" s="3"/>
+    </row>
+    <row r="90" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F90" s="3"/>
+      <c r="I90" s="3"/>
+      <c r="J90" s="3"/>
+    </row>
+    <row r="91" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F91" s="3"/>
+      <c r="I91" s="3"/>
+      <c r="J91" s="3"/>
+    </row>
+    <row r="92" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F92" s="3"/>
+      <c r="I92" s="3"/>
+      <c r="J92" s="3"/>
+    </row>
+    <row r="93" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F93" s="3"/>
+      <c r="I93" s="3"/>
+      <c r="J93" s="3"/>
+    </row>
+    <row r="94" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F94" s="3"/>
+      <c r="I94" s="3"/>
+      <c r="J94" s="3"/>
+    </row>
+    <row r="95" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F95" s="3"/>
+      <c r="I95" s="3"/>
+      <c r="J95" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1327,62 +2007,62 @@
   <dimension ref="B5:D10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11.42578125" style="5"/>
-    <col min="3" max="3" width="26.140625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="51.42578125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="3"/>
+    <col min="3" max="3" width="26.140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="51.42578125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="5" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="8"/>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="8" t="s">
+    </row>
+    <row r="6" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="8"/>
-      <c r="C6" s="8" t="s">
+      <c r="D6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>14</v>
-      </c>
     </row>
     <row r="7" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="8"/>
-      <c r="C7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>100</v>
+      <c r="B7" s="5"/>
+      <c r="C7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="8"/>
-      <c r="C8" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>64</v>
+      <c r="B8" s="5"/>
+      <c r="C8" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="63" x14ac:dyDescent="0.25">
-      <c r="B9" s="8"/>
-      <c r="C9" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>91</v>
+      <c r="B9" s="5"/>
+      <c r="C9" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="8"/>
-      <c r="C10" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" s="8"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AlcanceProducción.xlsx
+++ b/AlcanceProducción.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DONSSON\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8137C1FB-9302-425C-AA60-427E4F7167F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDDCEB02-28E8-49D8-8C3E-9C72C08D2052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F7EF0607-0985-4E51-B660-99D3760A7ED6}"/>
   </bookViews>
@@ -1557,7 +1557,7 @@
       <c r="I42" s="10"/>
       <c r="J42" s="10"/>
     </row>
-    <row r="43" spans="2:10" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:10" ht="104.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="10"/>
       <c r="C43" s="11" t="s">
         <v>82</v>
@@ -1571,7 +1571,6 @@
       <c r="F43" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="G43" s="15"/>
       <c r="H43" s="15"/>
       <c r="I43" s="10"/>
       <c r="J43" s="10"/>

--- a/AlcanceProducción.xlsx
+++ b/AlcanceProducción.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DONSSON\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDDCEB02-28E8-49D8-8C3E-9C72C08D2052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{551A7B57-D994-4649-8979-6B35703E1701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F7EF0607-0985-4E51-B660-99D3760A7ED6}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="FUNCIONALIDADES" sheetId="1" r:id="rId1"/>
     <sheet name="Diccionario " sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
